--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1250"/>
+  <dimension ref="A1:B1251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15428,6 +15428,18 @@
         </is>
       </c>
     </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>C82</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>YY.STUDIO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1251"/>
+  <dimension ref="A1:B1252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15440,6 +15440,18 @@
         </is>
       </c>
     </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>C83</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>韓尚</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1252"/>
+  <dimension ref="A1:B1253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15452,6 +15452,18 @@
         </is>
       </c>
     </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>C84</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>璇璇</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1253"/>
+  <dimension ref="A1:B1254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15464,6 +15464,18 @@
         </is>
       </c>
     </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>C85</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>開開家</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1254"/>
+  <dimension ref="A1:B1255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15476,6 +15476,18 @@
         </is>
       </c>
     </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>C86</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>喜樂</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1255"/>
+  <dimension ref="A1:B1256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15488,6 +15488,18 @@
         </is>
       </c>
     </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>C87</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>丹佳琪</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1256"/>
+  <dimension ref="A1:B1257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15500,6 +15500,18 @@
         </is>
       </c>
     </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>C88</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>木易子</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1257"/>
+  <dimension ref="A1:B1258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15512,6 +15512,18 @@
         </is>
       </c>
     </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>C89</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>AO!AO!</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1258"/>
+  <dimension ref="A1:B1259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15524,6 +15524,18 @@
         </is>
       </c>
     </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>C90</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -14963,7 +14963,7 @@
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>144</t>
         </is>
       </c>
       <c r="B1212" t="inlineStr">

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1259"/>
+  <dimension ref="A1:B1260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15536,6 +15536,18 @@
         </is>
       </c>
     </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>C92</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>划得來</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1260"/>
+  <dimension ref="A1:B1261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15548,6 +15548,18 @@
         </is>
       </c>
     </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>A36</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>芸尚+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1261"/>
+  <dimension ref="A1:B1262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15560,6 +15560,18 @@
         </is>
       </c>
     </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>C93</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>紫‧薇</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1262"/>
+  <dimension ref="A1:B1263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15572,6 +15572,18 @@
         </is>
       </c>
     </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>c94</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1263"/>
+  <dimension ref="A1:B1264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15584,6 +15584,18 @@
         </is>
       </c>
     </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>D.M大麥家</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1264"/>
+  <dimension ref="A1:B1265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15596,6 +15596,18 @@
         </is>
       </c>
     </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>C95</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>悠悠家</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1265"/>
+  <dimension ref="A1:B1266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15608,6 +15608,18 @@
         </is>
       </c>
     </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>C96</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>K.KSTUDIO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1266"/>
+  <dimension ref="A1:B1267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15620,6 +15620,18 @@
         </is>
       </c>
     </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>C97</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>軒衣閣</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1267"/>
+  <dimension ref="A1:B1268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15632,6 +15632,18 @@
         </is>
       </c>
     </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>C98</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>YT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1268"/>
+  <dimension ref="A1:B1269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15644,6 +15644,18 @@
         </is>
       </c>
     </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>C99</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>小果妮</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1269"/>
+  <dimension ref="A1:B1270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15656,6 +15656,18 @@
         </is>
       </c>
     </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>汐禾</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1270"/>
+  <dimension ref="A1:B1271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15668,6 +15668,18 @@
         </is>
       </c>
     </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>明珠</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/JB/廠商代碼.xlsx
+++ b/data/JB/廠商代碼.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1271"/>
+  <dimension ref="A1:B1272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15680,6 +15680,18 @@
         </is>
       </c>
     </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>惠惠家</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
